--- a/artfynd/A 26493-2024 artfynd.xlsx
+++ b/artfynd/A 26493-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115629046</v>
       </c>
       <c r="B2" t="n">
-        <v>97687</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115629050</v>
+        <v>115629048</v>
       </c>
       <c r="B3" t="n">
-        <v>97687</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>331309</v>
+        <v>331293</v>
       </c>
       <c r="R3" t="n">
-        <v>6423409</v>
+        <v>6423386</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,12 +885,7 @@
         <v>115629049</v>
       </c>
       <c r="B4" t="n">
-        <v>97687</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115629048</v>
+        <v>115629050</v>
       </c>
       <c r="B5" t="n">
-        <v>97687</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,7 +1013,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>331293</v>
+        <v>331309</v>
       </c>
       <c r="R5" t="n">
-        <v>6423386</v>
+        <v>6423409</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,12 +1087,7 @@
         <v>115629051</v>
       </c>
       <c r="B6" t="n">
-        <v>97687</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,12 +1188,7 @@
         <v>115629052</v>
       </c>
       <c r="B7" t="n">
-        <v>97687</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26493-2024 artfynd.xlsx
+++ b/artfynd/A 26493-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629046</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629048</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629049</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629050</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629051</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,8 +1313,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115629052</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>